--- a/CLH_Catalogue.xlsx
+++ b/CLH_Catalogue.xlsx
@@ -972,7 +972,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="200" customHeight="1" s="39">
+    <row r="26" ht="280" customHeight="1" s="39">
       <c r="B26" s="51" t="inlineStr">
         <is>
           <t>If you used v1.0 and are updating to v1.1, make these quick find-and-replace fixes in your Holdings tab:
@@ -990,7 +990,14 @@
   • 'PNC/PMC-Std' → 'PNC/PMC — Standard'
   • 'Other Carded' → 'Carded (Other)'
 Your data rows, titles, counts and all other fields are unaffected.
-Use Excel's Find &amp; Replace (Ctrl+H / Cmd+H) in the Holdings tab to make these changes quickly.</t>
+Use Excel's Find &amp; Replace (Ctrl+H / Cmd+H) in the Holdings tab to make these changes quickly.
+ENABLING SORT &amp; FILTER (v1.0 users only):
+If sort/filter arrows don't appear on the Holdings header row, fix it in 4 steps:
+  1. Go to Review → Unprotect Sheet (no password needed)
+  2. Click any cell in the Holdings header row (row 1)
+  3. Go to Data → Filter to turn on the dropdown arrows
+  4. Go to Review → Protect Sheet — tick 'Sort' and 'Use AutoFilter' before clicking OK
+Your data is completely untouched by this process.</t>
         </is>
       </c>
     </row>

--- a/CLH_Catalogue.xlsx
+++ b/CLH_Catalogue.xlsx
@@ -972,7 +972,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="280" customHeight="1" s="39">
+    <row r="26" ht="320" customHeight="1" s="39">
       <c r="B26" s="51" t="inlineStr">
         <is>
           <t>If you used v1.0 and are updating to v1.1, make these quick find-and-replace fixes in your Holdings tab:
@@ -997,7 +997,9 @@
   2. Click any cell in the Holdings header row (row 1)
   3. Go to Data → Filter to turn on the dropdown arrows
   4. Go to Review → Protect Sheet — tick 'Sort' and 'Use AutoFilter' before clicking OK
-Your data is completely untouched by this process.</t>
+Your data is completely untouched by this process.
+USING GOOGLE SHEETS?
+No action needed — Google Sheets ignores Excel sheet protection, so sorting and filtering work straight away. If filter arrows aren't visible, go to Data → Create a filter.</t>
         </is>
       </c>
     </row>
